--- a/education_forms/038_virtual_workshop_registration_form--education_forms.xlsx
+++ b/education_forms/038_virtual_workshop_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email (2)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>workshop_name</t>
+          <t>workshop_name_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>participant_status</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Confirm Participant</t>
+          <t>Confirm Participant (2)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>workshop_details</t>
+          <t>workshop_details_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>workshop_location</t>
+          <t>Workshop Details 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>workshop_name</t>
+          <t>workshop_name_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>workshop_name</t>
+          <t>Workshop Name 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>workshop_name_choices</t>
+          <t>workshop_name_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>workshop_name_choices</t>
+          <t>workshop_name_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_8_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_8_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_10_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_10_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_11_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>name_11_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
